--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N10_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0001T0006Z000C1N10_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.28143756481607</v>
+        <v>4.433233604282611</v>
       </c>
       <c r="D2" t="n">
-        <v>25.69710704045376</v>
+        <v>4.175779894073736</v>
       </c>
       <c r="E2" t="n">
-        <v>22.9812720466519</v>
+        <v>3.734456707580935</v>
       </c>
       <c r="F2" t="n">
-        <v>14.13538337845459</v>
+        <v>2.296999798998871</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>12.29582776897338</v>
+        <v>1.998072012458174</v>
       </c>
       <c r="D3" t="n">
-        <v>56.26794579844912</v>
+        <v>9.143541192247982</v>
       </c>
       <c r="E3" t="n">
-        <v>22.9812720466519</v>
+        <v>3.734456707580935</v>
       </c>
       <c r="F3" t="n">
-        <v>14.13538337845459</v>
+        <v>2.296999798998871</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>9.956932700072315</v>
+        <v>1.618001563761751</v>
       </c>
       <c r="D4" t="n">
-        <v>35.62818517788645</v>
+        <v>5.789580091406548</v>
       </c>
       <c r="E4" t="n">
-        <v>22.9812720466519</v>
+        <v>3.734456707580935</v>
       </c>
       <c r="F4" t="n">
-        <v>14.13538337845459</v>
+        <v>2.296999798998871</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.81231329462464</v>
+        <v>5.169500910376503</v>
       </c>
       <c r="D5" t="n">
-        <v>45.46843236835938</v>
+        <v>7.388620259858399</v>
       </c>
       <c r="E5" t="n">
-        <v>22.9812720466519</v>
+        <v>3.734456707580935</v>
       </c>
       <c r="F5" t="n">
-        <v>14.13538337845459</v>
+        <v>2.296999798998871</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.43773563251542</v>
+        <v>3.321132040283756</v>
       </c>
       <c r="D6" t="n">
-        <v>19.74355949212273</v>
+        <v>3.208328417469944</v>
       </c>
       <c r="E6" t="n">
-        <v>22.9812720466519</v>
+        <v>3.734456707580935</v>
       </c>
       <c r="F6" t="n">
-        <v>14.13538337845459</v>
+        <v>2.296999798998871</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>24.53492342362098</v>
+        <v>3.986925056338409</v>
       </c>
       <c r="D7" t="n">
-        <v>24.93186584344484</v>
+        <v>4.051428199559787</v>
       </c>
       <c r="E7" t="n">
-        <v>22.9812720466519</v>
+        <v>3.734456707580935</v>
       </c>
       <c r="F7" t="n">
-        <v>14.13538337845459</v>
+        <v>2.296999798998871</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.05817690568859</v>
+        <v>3.909453747174397</v>
       </c>
       <c r="D8" t="n">
-        <v>43.50994662411241</v>
+        <v>7.070366326418267</v>
       </c>
       <c r="E8" t="n">
-        <v>22.9812720466519</v>
+        <v>3.734456707580935</v>
       </c>
       <c r="F8" t="n">
-        <v>14.13538337845459</v>
+        <v>2.296999798998871</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>19.17899032609521</v>
+        <v>3.116585927990472</v>
       </c>
       <c r="D9" t="n">
-        <v>19.00489284027806</v>
+        <v>3.088295086545185</v>
       </c>
       <c r="E9" t="n">
-        <v>22.9812720466519</v>
+        <v>3.734456707580935</v>
       </c>
       <c r="F9" t="n">
-        <v>14.13538337845459</v>
+        <v>2.296999798998871</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>34.52136813069185</v>
+        <v>5.609722321237426</v>
       </c>
       <c r="D10" t="n">
-        <v>36.8591766400917</v>
+        <v>5.989616204014902</v>
       </c>
       <c r="E10" t="n">
-        <v>22.9812720466519</v>
+        <v>3.734456707580935</v>
       </c>
       <c r="F10" t="n">
-        <v>14.13538337845459</v>
+        <v>2.296999798998871</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>48.83515794157735</v>
+        <v>7.93571316550632</v>
       </c>
       <c r="D11" t="n">
-        <v>48.46648326421054</v>
+        <v>7.875803530434212</v>
       </c>
       <c r="E11" t="n">
-        <v>22.9812720466519</v>
+        <v>3.734456707580935</v>
       </c>
       <c r="F11" t="n">
-        <v>14.13538337845459</v>
+        <v>2.296999798998871</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>44.4976975652643</v>
+        <v>7.23087585435545</v>
       </c>
       <c r="D12" t="n">
-        <v>40.04996878900157</v>
+        <v>6.508119928212756</v>
       </c>
       <c r="E12" t="n">
-        <v>22.9812720466519</v>
+        <v>3.734456707580935</v>
       </c>
       <c r="F12" t="n">
-        <v>14.13538337845459</v>
+        <v>2.296999798998871</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>66.94228751621839</v>
+        <v>10.87812172138549</v>
       </c>
       <c r="D13" t="n">
-        <v>34.27339360680094</v>
+        <v>5.569426461105152</v>
       </c>
       <c r="E13" t="n">
-        <v>22.9812720466519</v>
+        <v>3.734456707580935</v>
       </c>
       <c r="F13" t="n">
-        <v>14.13538337845459</v>
+        <v>2.296999798998871</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>74.72059497152351</v>
+        <v>12.14209668287257</v>
       </c>
       <c r="D14" t="n">
-        <v>6.799225393560576</v>
+        <v>1.104874126453594</v>
       </c>
       <c r="E14" t="n">
-        <v>22.9812720466519</v>
+        <v>3.734456707580935</v>
       </c>
       <c r="F14" t="n">
-        <v>14.13538337845459</v>
+        <v>2.296999798998871</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>65.77325273683942</v>
+        <v>10.68815356973641</v>
       </c>
       <c r="D15" t="n">
-        <v>9.805820619703955</v>
+        <v>1.593445850701893</v>
       </c>
       <c r="E15" t="n">
-        <v>22.9812720466519</v>
+        <v>3.734456707580935</v>
       </c>
       <c r="F15" t="n">
-        <v>14.13538337845459</v>
+        <v>2.296999798998871</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>84.68779349936908</v>
+        <v>13.76176644364748</v>
       </c>
       <c r="D16" t="n">
-        <v>18</v>
+        <v>2.925</v>
       </c>
       <c r="E16" t="n">
-        <v>22.9812720466519</v>
+        <v>3.734456707580935</v>
       </c>
       <c r="F16" t="n">
-        <v>14.13538337845459</v>
+        <v>2.296999798998871</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
